--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>508.06</v>
+        <v>501.5</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9488.18</v>
+        <v>9365.540000000001</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2027.98</v>
+        <v>2002.22</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1066.25</v>
+        <v>1052.71</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9735.530000000001</v>
+        <v>9611.870000000001</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>701.8200000000001</v>
+        <v>692.91</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9735.530000000001</v>
+        <v>9611.870000000001</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>458.87</v>
+        <v>453.04</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9004.200000000001</v>
+        <v>8889.83</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>700.5</v>
+        <v>691.6</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8740.08</v>
+        <v>8629.059999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1153.22</v>
+        <v>1138.58</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8794.200000000001</v>
+        <v>8706.709999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>993.29</v>
+        <v>983.4</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7174.29</v>
+        <v>7102.91</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8312.48</v>
+        <v>8229.77</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>287.42</v>
+        <v>284.56</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>18976.35</v>
+        <v>18787.55</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>924</v>
+        <v>914.8099999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5325.99</v>
+        <v>5273</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3028.31</v>
+        <v>2998.18</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3286.18</v>
+        <v>3253.49</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>166.73</v>
+        <v>166.14</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>166.73</v>
+        <v>166.14</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>32917.37</v>
+        <v>32799.34</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2960.25</v>
+        <v>2949.64</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>700.5</v>
+        <v>697.99</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9572.459999999999</v>
+        <v>9538.139999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>166.73</v>
+        <v>166.14</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4145.69</v>
+        <v>4130.83</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8741</v>
+        <v>8709.66</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>492.28</v>
+        <v>490.51</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>8241.59</v>
+        <v>8212.040000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>20684.62</v>
+        <v>20610.45</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1267.5</v>
+        <v>1262.95</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7079.92</v>
+        <v>7064.59</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>776.48</v>
+        <v>774.8</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>6205.86</v>
+        <v>6192.43</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8359.32</v>
+        <v>8341.23</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1585.37</v>
+        <v>1581.94</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1830.78</v>
+        <v>1826.81</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>492.28</v>
+        <v>490.21</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>294.82</v>
+        <v>293.58</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8736.09</v>
+        <v>8699.459999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2597.79</v>
+        <v>2586.9</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13518.38</v>
+        <v>13461.71</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>18639.15</v>
+        <v>18561.01</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>14881.47</v>
+        <v>14709.25</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>16483.19</v>
+        <v>16292.42</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8324.76</v>
+        <v>8228.42</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>764.21</v>
+        <v>755.36</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8794.200000000001</v>
+        <v>8692.43</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>997.64</v>
+        <v>986.1</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>34944.35</v>
+        <v>34539.93</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4460.58</v>
+        <v>4408.95</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>9572.459999999999</v>
+        <v>9461.68</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>458.87</v>
+        <v>453.56</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8736.09</v>
+        <v>8634.98</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8323.879999999999</v>
+        <v>8227.549999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>458.87</v>
+        <v>453.56</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8741</v>
+        <v>8639.84</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>17856.96</v>
+        <v>17650.3</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>647.1</v>
+        <v>639.61</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>35044.2</v>
+        <v>34747.35</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>156.67</v>
+        <v>155.34</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>641.36</v>
+        <v>635.92</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>37621.47</v>
+        <v>37591.23</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3052.4</v>
+        <v>3049.95</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>9488.18</v>
+        <v>9480.549999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8323.879999999999</v>
+        <v>8317.190000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>535.13</v>
+        <v>534.7</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>8947.91</v>
+        <v>8940.719999999999</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>612.33</v>
+        <v>611.83</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>9735.15</v>
+        <v>9727.32</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>9488.18</v>
+        <v>9480.549999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>26824.46</v>
+        <v>26802.9</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>28979.72</v>
+        <v>28956.43</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>7074.43</v>
+        <v>7068.75</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1149.17</v>
+        <v>1148.25</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1829.7</v>
+        <v>1828.23</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>551.98</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>490.03</v>
+        <v>491.91</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>9137.75</v>
+        <v>9172.82</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>18480.9</v>
+        <v>18551.84</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>980.05</v>
+        <v>983.8099999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>8241.59</v>
+        <v>8278.940000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>450.81</v>
+        <v>452.85</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8794.200000000001</v>
+        <v>8834.059999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>450.81</v>
+        <v>452.85</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8811.219999999999</v>
+        <v>8851.15</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>757.2</v>
+        <v>760.63</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>9735.15</v>
+        <v>9779.26</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>18955.67</v>
+        <v>19041.57</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8312.48</v>
+        <v>8350.15</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>855.85</v>
+        <v>858.12</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>475.26</v>
+        <v>476.52</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>328.3</v>
+        <v>329.17</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>142.99</v>
+        <v>143.37</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>856.17</v>
+        <v>858.4400000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5767.72</v>
+        <v>5783.01</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>37351.56</v>
+        <v>37450.61</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>37105.55</v>
+        <v>37203.94</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1213.84</v>
+        <v>1212.13</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>814.8099999999999</v>
+        <v>813.67</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>10478.35</v>
+        <v>10463.65</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2954.99</v>
+        <v>2958.78</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2109.06</v>
+        <v>2111.76</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>73699.33</v>
+        <v>73793.81</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8241.59</v>
+        <v>8298.32</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1000.87</v>
+        <v>1007.76</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>17480.15</v>
+        <v>17600.47</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>337.49</v>
+        <v>339.81</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1606.06</v>
+        <v>1617.11</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>333.47</v>
+        <v>335.76</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>854.85</v>
+        <v>860.74</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>492.28</v>
+        <v>495.66</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>8241.59</v>
+        <v>8298.32</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>17622.45</v>
+        <v>17743.75</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1470.08</v>
+        <v>1480.19</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1221.36</v>
+        <v>1229.76</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>24105.53</v>
+        <v>24271.45</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4225.84</v>
+        <v>4254.93</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1184.7</v>
+        <v>1192.86</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>8312.48</v>
+        <v>8369.690000000001</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8741</v>
+        <v>8801.16</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>56782.52</v>
+        <v>57173.36</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>521.79</v>
+        <v>526.25</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>8237.030000000001</v>
+        <v>8307.42</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3302.7</v>
+        <v>3330.93</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>90429.50999999999</v>
+        <v>91202.3</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>19144.93</v>
+        <v>19308.54</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>6017.52</v>
+        <v>6068.95</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>572.38</v>
+        <v>578.52</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>980.05</v>
+        <v>990.5599999999999</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>407.12</v>
+        <v>411.49</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>16070.35</v>
+        <v>16242.73</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>13383.84</v>
+        <v>13527.4</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>19118.7</v>
+        <v>19323.78</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>9488.18</v>
+        <v>9589.950000000001</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>15762.7</v>
+        <v>15931.78</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1126.53</v>
+        <v>1138.62</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5492.34</v>
+        <v>5551.25</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3855.23</v>
+        <v>3896.58</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>11255.38</v>
+        <v>11376.12</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5426.46</v>
+        <v>5484.67</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1355.06</v>
+        <v>1369.59</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>687.85</v>
+        <v>695.23</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2516.12</v>
+        <v>2548.45</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>4978.02</v>
+        <v>5005.24</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>458.87</v>
+        <v>461.38</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>8740</v>
+        <v>8787.790000000001</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>8241.59</v>
+        <v>8286.66</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>589.1</v>
+        <v>592.33</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8740</v>
+        <v>8787.790000000001</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>922.58</v>
+        <v>927.63</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8740</v>
+        <v>8787.790000000001</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>330.86</v>
+        <v>332.67</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>932.54</v>
+        <v>937.64</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>458.87</v>
+        <v>461.38</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>8947.91</v>
+        <v>8996.84</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9078.24</v>
+        <v>9127.889999999999</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7593.67</v>
+        <v>7635.2</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>166.73</v>
+        <v>167.65</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4670.93</v>
+        <v>4696.48</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>9458.23</v>
+        <v>9509.959999999999</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1679.47</v>
+        <v>1688.66</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/dic-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1570,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1948,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2013,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2200,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2326,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2391,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2456,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2521,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2708,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2773,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2838,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2903,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2968,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3094,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3159,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3224,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3350,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3476,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3541,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3728,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3854,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4102,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4289,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4354,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4602,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4789,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5403,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5529,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5655,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5964,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6090,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6521,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6586,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6651,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6716,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6842,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6907,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6972,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7098,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7163,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7411,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7537,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7663,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7728,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7793,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8224,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8350,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8415,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8480,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8854,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9407,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9472,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9537,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9602,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9667,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9732,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9858,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +9923,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10110,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10236,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10423,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10488,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10736,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +10801,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +10866,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +10931,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
